--- a/data/cemetery/data.xlsx
+++ b/data/cemetery/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -479,19 +479,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="str">
-        <v>34.3315625</v>
+        <v>34.33149194</v>
       </c>
       <c r="C4" t="str">
-        <v>134.03373833</v>
+        <v>134.03561667</v>
       </c>
       <c r="D4" t="str">
-        <v>高松市姥ヶ池西墓地</v>
+        <v>高松市姥ヶ池東墓地</v>
       </c>
       <c r="E4" t="str">
-        <v>高松市宮脇町二丁目998</v>
+        <v>高松市宮脇町二丁目10-56</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -505,19 +505,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="str">
-        <v>34.33149194</v>
+        <v>34.33382833</v>
       </c>
       <c r="C5" t="str">
-        <v>134.03561667</v>
+        <v>134.03325583</v>
       </c>
       <c r="D5" t="str">
-        <v>高松市姥ヶ池東墓地</v>
+        <v>高松市紫雲墓地</v>
       </c>
       <c r="E5" t="str">
-        <v>高松市宮脇町二丁目10-56</v>
+        <v>高松市宮脇町二丁目994-25</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -531,19 +531,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="str">
-        <v>34.33382833</v>
+        <v>34.33657194</v>
       </c>
       <c r="C6" t="str">
-        <v>134.03325583</v>
+        <v>134.0283425</v>
       </c>
       <c r="D6" t="str">
-        <v>高松市紫雲墓地</v>
+        <v>高松市峰山墓地</v>
       </c>
       <c r="E6" t="str">
-        <v>高松市宮脇町二丁目994-25</v>
+        <v>高松市西宝町二丁目844-43</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -557,19 +557,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="str">
-        <v>34.33657194</v>
+        <v>34.33920444</v>
       </c>
       <c r="C7" t="str">
-        <v>134.0283425</v>
+        <v>134.02993083</v>
       </c>
       <c r="D7" t="str">
-        <v>高松市峰山墓地</v>
+        <v>高松市本門院墓地</v>
       </c>
       <c r="E7" t="str">
-        <v>高松市西宝町二丁目844-43</v>
+        <v>高松市西宝町二丁目4-4</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -583,19 +583,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" t="str">
-        <v>34.33920444</v>
+        <v>34.32480861</v>
       </c>
       <c r="C8" t="str">
-        <v>134.02993083</v>
+        <v>134.05303194</v>
       </c>
       <c r="D8" t="str">
-        <v>高松市本門院墓地</v>
+        <v>高松市柳三昧墓地</v>
       </c>
       <c r="E8" t="str">
-        <v>高松市西宝町二丁目4-4</v>
+        <v>高松市桜町二丁目17-3</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -609,19 +609,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" t="str">
-        <v>34.32467833</v>
+        <v>34.3304175</v>
       </c>
       <c r="C9" t="str">
-        <v>134.05362</v>
+        <v>134.05996306</v>
       </c>
       <c r="D9" t="str">
-        <v>高松市柳三昧北墓地</v>
+        <v>高松市楠川墓地</v>
       </c>
       <c r="E9" t="str">
-        <v>高松市桜町二丁目17-3</v>
+        <v>高松市上福岡町2003-7</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -635,19 +635,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" t="str">
-        <v>34.32480861</v>
+        <v>34.34066083</v>
       </c>
       <c r="C10" t="str">
-        <v>134.05303194</v>
+        <v>134.07439333</v>
       </c>
       <c r="D10" t="str">
-        <v>高松市柳三昧墓地</v>
+        <v>高松市沖松島墓地</v>
       </c>
       <c r="E10" t="str">
-        <v>高松市桜町二丁目15-37</v>
+        <v>高松市福岡町四丁目35-20</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -661,19 +661,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" t="str">
-        <v>34.3304175</v>
+        <v>34.3418</v>
       </c>
       <c r="C11" t="str">
-        <v>134.05996306</v>
+        <v>134.12916472</v>
       </c>
       <c r="D11" t="str">
-        <v>高松市楠川墓地</v>
+        <v>高松市西林寺墓地</v>
       </c>
       <c r="E11" t="str">
-        <v>高松市上福岡町2003-7</v>
+        <v>高松市牟礼町牟礼917-2</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -687,19 +687,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" t="str">
-        <v>34.34066083</v>
+        <v>34.34517028</v>
       </c>
       <c r="C12" t="str">
-        <v>134.07439333</v>
+        <v>134.1356975</v>
       </c>
       <c r="D12" t="str">
-        <v>高松市沖松島墓地</v>
+        <v>高松市岡ノ山墓地</v>
       </c>
       <c r="E12" t="str">
-        <v>高松市福岡町四丁目35-20</v>
+        <v>高松市牟礼町牟礼1307</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -713,19 +713,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" t="str">
-        <v>34.3418</v>
+        <v>34.34401583</v>
       </c>
       <c r="C13" t="str">
-        <v>134.12916472</v>
+        <v>134.14260111</v>
       </c>
       <c r="D13" t="str">
-        <v>高松市西林寺墓地</v>
+        <v>高松市田井墓地</v>
       </c>
       <c r="E13" t="str">
-        <v>高松市牟礼町牟礼917-2</v>
+        <v>高松市牟礼町牟礼1587-9</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -739,19 +739,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" t="str">
-        <v>34.34517028</v>
+        <v>34.35120639</v>
       </c>
       <c r="C14" t="str">
-        <v>134.1356975</v>
+        <v>134.13687389</v>
       </c>
       <c r="D14" t="str">
-        <v>高松市岡ノ山墓地</v>
+        <v>高松市松井谷墓地</v>
       </c>
       <c r="E14" t="str">
-        <v>高松市牟礼町牟礼1307</v>
+        <v>高松市牟礼町牟礼1701-1</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -765,19 +765,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" t="str">
-        <v>34.34401583</v>
+        <v>34.36187389</v>
       </c>
       <c r="C15" t="str">
-        <v>134.14260111</v>
+        <v>134.12934306</v>
       </c>
       <c r="D15" t="str">
-        <v>高松市田井墓地</v>
+        <v>高松市久通墓地</v>
       </c>
       <c r="E15" t="str">
-        <v>高松市牟礼町牟礼1587-9</v>
+        <v>高松市牟礼町牟礼3442-14</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -791,19 +791,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" t="str">
-        <v>34.35120639</v>
+        <v>34.34025306</v>
       </c>
       <c r="C16" t="str">
-        <v>134.13687389</v>
+        <v>134.14746639</v>
       </c>
       <c r="D16" t="str">
-        <v>高松市松井谷墓地</v>
+        <v>高松市焼野墓地</v>
       </c>
       <c r="E16" t="str">
-        <v>高松市牟礼町牟礼1701-1</v>
+        <v>高松市牟礼町大町626</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -817,19 +817,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" t="str">
-        <v>34.36187389</v>
+        <v>34.33885194</v>
       </c>
       <c r="C17" t="str">
-        <v>134.12934306</v>
+        <v>134.15394583</v>
       </c>
       <c r="D17" t="str">
-        <v>高松市久通墓地</v>
+        <v>高松市北三昧墓地</v>
       </c>
       <c r="E17" t="str">
-        <v>高松市牟礼町牟礼3442-14</v>
+        <v>高松市牟礼町大町985</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -843,19 +843,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" t="str">
-        <v>34.34025306</v>
+        <v>34.33742056</v>
       </c>
       <c r="C18" t="str">
-        <v>134.14746639</v>
+        <v>134.15526861</v>
       </c>
       <c r="D18" t="str">
-        <v>高松市焼野墓地</v>
+        <v>高松市南三昧墓地</v>
       </c>
       <c r="E18" t="str">
-        <v>高松市牟礼町大町626</v>
+        <v>高松市牟礼町大町1005</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -869,19 +869,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" t="str">
-        <v>34.33885194</v>
+        <v>34.33905556</v>
       </c>
       <c r="C19" t="str">
-        <v>134.15394583</v>
+        <v>134.14246056</v>
       </c>
       <c r="D19" t="str">
-        <v>高松市北三昧墓地</v>
+        <v>高松市焼背ヶ原墓地</v>
       </c>
       <c r="E19" t="str">
-        <v>高松市牟礼町大町985</v>
+        <v>高松市牟礼町大町2420</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -895,19 +895,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" t="str">
-        <v>34.33742056</v>
+        <v>34.33524139</v>
       </c>
       <c r="C20" t="str">
-        <v>134.15526861</v>
+        <v>134.14622944</v>
       </c>
       <c r="D20" t="str">
-        <v>高松市南三昧墓地</v>
+        <v>高松市鐙田墓地</v>
       </c>
       <c r="E20" t="str">
-        <v>高松市牟礼町大町1005</v>
+        <v>高松市牟礼町大町2442-1</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -921,19 +921,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" t="str">
-        <v>34.33905556</v>
+        <v>34.33538972</v>
       </c>
       <c r="C21" t="str">
-        <v>134.14246056</v>
+        <v>134.13418056</v>
       </c>
       <c r="D21" t="str">
-        <v>高松市焼背ヶ原墓地</v>
+        <v>高松市丹僧墓地</v>
       </c>
       <c r="E21" t="str">
-        <v>高松市牟礼町大町2420</v>
+        <v>高松市牟礼町大町2560</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -947,19 +947,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22" t="str">
-        <v>34.33524139</v>
+        <v>34.32106667</v>
       </c>
       <c r="C22" t="str">
-        <v>134.14622944</v>
+        <v>134.16079667</v>
       </c>
       <c r="D22" t="str">
-        <v>高松市鐙田墓地</v>
+        <v>高松市浜三昧墓地</v>
       </c>
       <c r="E22" t="str">
-        <v>高松市牟礼町大町2442-1</v>
+        <v>高松市牟礼町原210-6</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -973,19 +973,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B23" t="str">
-        <v>34.33538972</v>
+        <v>34.32632611</v>
       </c>
       <c r="C23" t="str">
-        <v>134.13418056</v>
+        <v>134.15213611</v>
       </c>
       <c r="D23" t="str">
-        <v>高松市丹僧墓地</v>
+        <v>高松市鋸ノ鼻墓地</v>
       </c>
       <c r="E23" t="str">
-        <v>高松市牟礼町大町2560</v>
+        <v>高松市牟礼町原1515</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -999,19 +999,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" t="str">
-        <v>34.32106667</v>
+        <v>34.38980139</v>
       </c>
       <c r="C24" t="str">
-        <v>134.16079667</v>
+        <v>134.13678972</v>
       </c>
       <c r="D24" t="str">
-        <v>高松市浜三昧墓地</v>
+        <v>高松市北村共同墓地</v>
       </c>
       <c r="E24" t="str">
-        <v>高松市牟礼町原210-6</v>
+        <v>高松市庵治町1443</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -1025,19 +1025,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25" t="str">
-        <v>34.32632611</v>
+        <v>34.25910528</v>
       </c>
       <c r="C25" t="str">
-        <v>134.15213611</v>
+        <v>134.04868639</v>
       </c>
       <c r="D25" t="str">
-        <v>高松市鋸ノ鼻墓地</v>
+        <v>高松市浅野墓地公園</v>
       </c>
       <c r="E25" t="str">
-        <v>高松市牟礼町原1515</v>
+        <v>高松市香川町浅野2845</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -1051,19 +1051,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" t="str">
-        <v>34.38980139</v>
+        <v>34.30312111</v>
       </c>
       <c r="C26" t="str">
-        <v>134.13678972</v>
+        <v>133.97368083</v>
       </c>
       <c r="D26" t="str">
-        <v>高松市北村共同墓地</v>
+        <v>高松市新居大谷公園墓地</v>
       </c>
       <c r="E26" t="str">
-        <v>高松市庵治町1443</v>
+        <v>高松市国分寺町新居223-1</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -1077,19 +1077,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B27" t="str">
-        <v>34.25910528</v>
+        <v>34.31440028</v>
       </c>
       <c r="C27" t="str">
-        <v>134.04868639</v>
+        <v>133.95901361</v>
       </c>
       <c r="D27" t="str">
-        <v>高松市浅野墓地公園</v>
+        <v>高松市川西公園墓地</v>
       </c>
       <c r="E27" t="str">
-        <v>高松市香川町浅野2845</v>
+        <v>高松市国分寺町新居3845-1</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1103,22 +1103,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B28" t="str">
-        <v>34.30312111</v>
+        <v>34.26100722</v>
       </c>
       <c r="C28" t="str">
-        <v>133.97368083</v>
+        <v>134.07571056</v>
       </c>
       <c r="D28" t="str">
-        <v>高松市新居大谷公園墓地</v>
+        <v>高松市平和公園</v>
       </c>
       <c r="E28" t="str">
-        <v>高松市国分寺町新居223-1</v>
+        <v>高松市三谷町2851-1</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>087-889-0938</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1129,25 +1129,25 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" t="str">
-        <v>34.31440028</v>
+        <v>34.26025278</v>
       </c>
       <c r="C29" t="str">
-        <v>133.95901361</v>
+        <v>134.0761375</v>
       </c>
       <c r="D29" t="str">
-        <v>高松市川西公園墓地</v>
+        <v>高松市平和公園合葬式墓地</v>
       </c>
       <c r="E29" t="str">
-        <v>高松市国分寺町新居3845-1</v>
+        <v>高松市三谷町2851-1</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>087-889-0938</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/bochi/about/moushikomi.html</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -1155,85 +1155,33 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B30" t="str">
-        <v>34.26100722</v>
+        <v>34.28977556</v>
       </c>
       <c r="C30" t="str">
-        <v>134.07571056</v>
+        <v>133.97270611</v>
       </c>
       <c r="D30" t="str">
-        <v>高松市平和公園</v>
+        <v>高松市六ツ目公園</v>
       </c>
       <c r="E30" t="str">
-        <v>高松市三谷町2851-1</v>
+        <v>高松市国分寺町福家乙39-1</v>
       </c>
       <c r="F30" t="str">
-        <v>087-889-0938</v>
+        <v/>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>30</v>
-      </c>
-      <c r="B31" t="str">
-        <v>34.26025278</v>
-      </c>
-      <c r="C31" t="str">
-        <v>134.0761375</v>
-      </c>
-      <c r="D31" t="str">
-        <v>高松市平和公園合葬式墓地</v>
-      </c>
-      <c r="E31" t="str">
-        <v>高松市三谷町2851-1</v>
-      </c>
-      <c r="F31" t="str">
-        <v>087-889-0938</v>
-      </c>
-      <c r="G31" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/bochi/about/moushikomi.html</v>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
-        <v>34.28977556</v>
-      </c>
-      <c r="C32" t="str">
-        <v>133.97270611</v>
-      </c>
-      <c r="D32" t="str">
-        <v>高松市六ツ目公園</v>
-      </c>
-      <c r="E32" t="str">
-        <v>高松市国分寺町福家39-1</v>
-      </c>
-      <c r="F32" t="str">
-        <v/>
-      </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
-      <c r="H32" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H30"/>
   </ignoredErrors>
 </worksheet>
 </file>